--- a/input/selectlist_268.xlsx
+++ b/input/selectlist_268.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC83C47-843D-42A7-B6A5-AB9321488BEE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA8203A-2BE1-4315-BC0C-C3D6EA6DB0D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9012" xr2:uid="{8EFC6329-1B1D-4247-998B-325220D9F705}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="534">
   <si>
     <t>A股代码</t>
   </si>
@@ -562,9 +562,6 @@
     <t>002737</t>
   </si>
   <si>
-    <t>葵花药业</t>
-  </si>
-  <si>
     <t>002756</t>
   </si>
   <si>
@@ -803,12 +800,6 @@
   </si>
   <si>
     <t>亿联网络</t>
-  </si>
-  <si>
-    <t>300630</t>
-  </si>
-  <si>
-    <t>普利退</t>
   </si>
   <si>
     <t>300638</t>
@@ -1653,6 +1644,10 @@
   </si>
   <si>
     <t>中国神华</t>
+  </si>
+  <si>
+    <t>葵花药业</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2032,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A0555C-0A9A-418C-B5BA-60D486A3FBE8}">
-  <dimension ref="A1:D270"/>
+  <dimension ref="A1:D269"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -2744,1472 +2739,1464 @@
         <v>177</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>178</v>
+        <v>533</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>411</v>
+        <v>531</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>534</v>
+        <v>411</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>519</v>
-      </c>
+      <c r="C259" s="3"/>
+      <c r="D259" s="1"/>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>521</v>
       </c>
       <c r="C260" s="3"/>
       <c r="D260" s="1"/>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="C261" s="3"/>
       <c r="D261" s="1"/>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="C262" s="3"/>
       <c r="D262" s="1"/>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A263" s="3" t="s">
-        <v>526</v>
+      <c r="A263" s="3">
+        <v>601088</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C263" s="3"/>
       <c r="D263" s="1"/>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A264" s="3">
-        <v>601088</v>
+      <c r="A264" s="3" t="s">
+        <v>525</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="C264" s="3"/>
+        <v>526</v>
+      </c>
+      <c r="C264" s="1"/>
       <c r="D264" s="1"/>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C265" s="1"/>
+      <c r="C265" s="3"/>
       <c r="D265" s="1"/>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>531</v>
       </c>
       <c r="C266" s="3"/>
       <c r="D266" s="1"/>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="C267" s="3"/>
       <c r="D267" s="1"/>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="3" t="s">
-        <v>516</v>
+      <c r="A268" s="3">
+        <v>600900</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>517</v>
+        <v>2</v>
       </c>
       <c r="C268" s="3"/>
       <c r="D268" s="1"/>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A269" s="3">
-        <v>600900</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C269" s="3"/>
+      <c r="C269" s="1"/>
       <c r="D269" s="1"/>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C270" s="1"/>
-      <c r="D270" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
